--- a/docs/sample-output/14-master-planned-3-phase/estimate.xlsx
+++ b/docs/sample-output/14-master-planned-3-phase/estimate.xlsx
@@ -21,7 +21,7 @@
     <t>FINISHES SOLUTIONS</t>
   </si>
   <si>
-    <t>Total Project Cost — Summary   ·   Brazos Crossing — 3-phase master plan · Total $170,314,234</t>
+    <t>Total Project Cost — Summary   ·   Brazos Crossing — 3-phase master plan · Total $168,894,726</t>
   </si>
   <si>
     <t>COST SUMMARY</t>
@@ -90,7 +90,7 @@
     <t>Research data version</t>
   </si>
   <si>
-    <t>2026.7c60a42879</t>
+    <t>2026.0c737c8255</t>
   </si>
   <si>
     <t>Engine</t>
@@ -99,10 +99,10 @@
     <t>budget-engine-2.0.0</t>
   </si>
   <si>
-    <t>All defaults come from the research data shipped with the app (2026.7c60a42879), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
-  </si>
-  <si>
-    <t>Cost by Component   ·   Brazos Crossing — 3-phase master plan · Total $170,314,234</t>
+    <t>All defaults come from the research data shipped with the app (2026.0c737c8255), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
+  </si>
+  <si>
+    <t>Cost by Component   ·   Brazos Crossing — 3-phase master plan · Total $168,894,726</t>
   </si>
   <si>
     <t>Component</t>
@@ -228,7 +228,7 @@
     <t>Garden apartments $1,101,129; Rental townhomes $367,043</t>
   </si>
   <si>
-    <t>Cost by Phase   ·   Brazos Crossing — 3-phase master plan · Total $170,314,234</t>
+    <t>Cost by Phase   ·   Brazos Crossing — 3-phase master plan · Total $168,894,726</t>
   </si>
   <si>
     <t>Phase</t>
@@ -294,7 +294,7 @@
     <t>21.1%</t>
   </si>
   <si>
-    <t>Line-Item Detail   ·   Brazos Crossing — 3-phase master plan · Total $170,314,234</t>
+    <t>Line-Item Detail   ·   Brazos Crossing — 3-phase master plan · Total $168,894,726</t>
   </si>
   <si>
     <t>Group</t>
@@ -663,7 +663,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Draw Schedules   ·   Brazos Crossing — 3-phase master plan · Total $170,314,234</t>
+    <t>Draw Schedules   ·   Brazos Crossing — 3-phase master plan · Total $168,894,726</t>
   </si>
   <si>
     <t>PHASE 1 — INFRASTRUCTURE + APARTMENTS — MONTHLY DRAWS</t>
@@ -846,7 +846,7 @@
     <t>2032-02</t>
   </si>
   <si>
-    <t>Sources &amp; Assumptions   ·   Brazos Crossing — 3-phase master plan · Total $170,314,234</t>
+    <t>Sources &amp; Assumptions   ·   Brazos Crossing — 3-phase master plan · Total $168,894,726</t>
   </si>
   <si>
     <t>ASSUMPTIONS</t>
@@ -2581,7 +2581,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="5">
-        <v>7011058.45</v>
+        <v>5741031.26</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2589,7 +2589,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="5">
-        <v>4781769.74</v>
+        <v>4758332.43</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2597,7 +2597,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="5">
-        <v>5446337.24</v>
+        <v>5383795.44</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2605,7 +2605,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="5">
-        <v>1258188.67</v>
+        <v>1194687.31</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2613,7 +2613,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="7">
-        <v>36844521.19</v>
+        <v>35425013.53</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2629,7 +2629,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="7">
-        <v>170314234.04</v>
+        <v>168894726.38</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2668,7 +2668,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="5">
-        <v>2747003.7748387097</v>
+        <v>2724108.4899999998</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2796,19 +2796,19 @@
         <v>61247111.97</v>
       </c>
       <c r="E5" s="13">
-        <v>20605772.98</v>
+        <v>20061092.81</v>
       </c>
       <c r="F5" s="13">
         <v>5219172.5</v>
       </c>
       <c r="G5" s="13">
-        <v>87072057.45</v>
+        <v>86527377.28</v>
       </c>
       <c r="H5" s="13">
-        <v>290240.1915</v>
+        <v>288424.5909333333</v>
       </c>
       <c r="I5" s="14">
-        <v>276.41923</v>
+        <v>274.6900866031746</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>42</v>
@@ -2828,19 +2828,19 @@
         <v>24093252.86</v>
       </c>
       <c r="E6" s="13">
-        <v>6153275.34</v>
+        <v>5381158.82</v>
       </c>
       <c r="F6" s="13">
         <v>2551595.44</v>
       </c>
       <c r="G6" s="13">
-        <v>32798123.64</v>
+        <v>32026007.12</v>
       </c>
       <c r="H6" s="13">
-        <v>409976.5455</v>
+        <v>400325.08900000004</v>
       </c>
       <c r="I6" s="14">
-        <v>227.7647475</v>
+        <v>222.40282722222224</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>46</v>
@@ -2860,19 +2860,19 @@
         <v>15417681.58</v>
       </c>
       <c r="E7" s="13">
-        <v>4343533.14</v>
+        <v>4291722.95</v>
       </c>
       <c r="F7" s="13">
         <v>2487805.56</v>
       </c>
       <c r="G7" s="13">
-        <v>22249020.28</v>
+        <v>22197210.09</v>
       </c>
       <c r="H7" s="13">
-        <v>342.2926196923077</v>
+        <v>341.49553984615386</v>
       </c>
       <c r="I7" s="14">
-        <v>342.2926196923077</v>
+        <v>341.49553984615386</v>
       </c>
       <c r="J7" s="12" t="s">
         <v>50</v>
@@ -2892,19 +2892,19 @@
         <v>21611066.44</v>
       </c>
       <c r="E8" s="13">
-        <v>5741939.73</v>
+        <v>5691038.95</v>
       </c>
       <c r="F8" s="13">
         <v>842026.5</v>
       </c>
       <c r="G8" s="13">
-        <v>28195032.67</v>
+        <v>28144131.89</v>
       </c>
       <c r="H8" s="13">
-        <v>256318.47881818184</v>
+        <v>255855.74445454546</v>
       </c>
       <c r="I8" s="14">
-        <v>413.4169013196481</v>
+        <v>412.6705555718475</v>
       </c>
       <c r="J8" s="12" t="s">
         <v>53</v>
@@ -2920,13 +2920,13 @@
         <v>122369112.85</v>
       </c>
       <c r="E9" s="16">
-        <v>36844521.19</v>
+        <v>35425013.53</v>
       </c>
       <c r="F9" s="16">
         <v>11100600</v>
       </c>
       <c r="G9" s="16">
-        <v>170314234.04</v>
+        <v>168894726.38</v>
       </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
@@ -3127,19 +3127,19 @@
         <v>65124220.17</v>
       </c>
       <c r="G5" s="13">
-        <v>21468482.69</v>
+        <v>20923231.17</v>
       </c>
       <c r="H5" s="13">
         <v>5219172.5</v>
       </c>
       <c r="I5" s="13">
-        <v>91811875.36</v>
+        <v>91266623.84</v>
       </c>
       <c r="J5" s="13">
-        <v>55087125.22</v>
+        <v>54759974.3</v>
       </c>
       <c r="K5" s="13">
-        <v>2888303.73</v>
+        <v>2860560.06</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -3162,19 +3162,19 @@
         <v>36149566.52</v>
       </c>
       <c r="G6" s="13">
-        <v>9760515.44</v>
+        <v>8937082.68</v>
       </c>
       <c r="H6" s="13">
         <v>5039401</v>
       </c>
       <c r="I6" s="13">
-        <v>50949482.96</v>
+        <v>50126050.2</v>
       </c>
       <c r="J6" s="13">
-        <v>30569689.78</v>
+        <v>30075630.12</v>
       </c>
       <c r="K6" s="13">
-        <v>908513.23</v>
+        <v>884040.97</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -3197,19 +3197,19 @@
         <v>21095326.16</v>
       </c>
       <c r="G7" s="13">
-        <v>5615523.06</v>
+        <v>5564699.68</v>
       </c>
       <c r="H7" s="13">
         <v>842026.5</v>
       </c>
       <c r="I7" s="13">
-        <v>27552875.72</v>
+        <v>27502052.34</v>
       </c>
       <c r="J7" s="13">
-        <v>16531725.43</v>
+        <v>16501231.4</v>
       </c>
       <c r="K7" s="13">
-        <v>627634.88</v>
+        <v>625826.06</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -3224,13 +3224,13 @@
         <v>122369112.85</v>
       </c>
       <c r="G8" s="16">
-        <v>36844521.19</v>
+        <v>35425013.53</v>
       </c>
       <c r="H8" s="16">
         <v>11100600</v>
       </c>
       <c r="I8" s="16">
-        <v>170314234.04</v>
+        <v>168894726.38</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
@@ -7059,10 +7059,10 @@
         <v>195</v>
       </c>
       <c r="H132" s="14">
-        <v>4838.18</v>
+        <v>3407.22</v>
       </c>
       <c r="I132" s="13">
-        <v>82490.97</v>
+        <v>58093.1</v>
       </c>
       <c r="J132" s="12" t="s">
         <v>104</v>
@@ -7091,10 +7091,10 @@
         <v>195</v>
       </c>
       <c r="H133" s="14">
-        <v>4592.44</v>
+        <v>3407.22</v>
       </c>
       <c r="I133" s="13">
-        <v>78301.1</v>
+        <v>58093.1</v>
       </c>
       <c r="J133" s="12" t="s">
         <v>104</v>
@@ -7547,10 +7547,10 @@
         <v>195</v>
       </c>
       <c r="H148" s="14">
-        <v>4838.18</v>
+        <v>3407.22</v>
       </c>
       <c r="I148" s="13">
-        <v>870872.4</v>
+        <v>613299.6</v>
       </c>
       <c r="J148" s="12" t="s">
         <v>104</v>
@@ -7579,10 +7579,10 @@
         <v>195</v>
       </c>
       <c r="H149" s="14">
-        <v>4592.44</v>
+        <v>3407.22</v>
       </c>
       <c r="I149" s="13">
-        <v>826639.2</v>
+        <v>613299.6</v>
       </c>
       <c r="J149" s="12" t="s">
         <v>104</v>
@@ -8395,10 +8395,10 @@
         <v>195</v>
       </c>
       <c r="H176" s="14">
-        <v>4838.18</v>
+        <v>3407.22</v>
       </c>
       <c r="I176" s="13">
-        <v>78620.43</v>
+        <v>55367.33</v>
       </c>
       <c r="J176" s="12" t="s">
         <v>104</v>
@@ -8427,10 +8427,10 @@
         <v>195</v>
       </c>
       <c r="H177" s="14">
-        <v>4592.44</v>
+        <v>3407.22</v>
       </c>
       <c r="I177" s="13">
-        <v>74627.15</v>
+        <v>55367.33</v>
       </c>
       <c r="J177" s="12" t="s">
         <v>104</v>
@@ -9211,10 +9211,10 @@
         <v>150</v>
       </c>
       <c r="H203" s="14">
-        <v>13214.69</v>
+        <v>6930.92</v>
       </c>
       <c r="I203" s="13">
-        <v>1057175.2</v>
+        <v>554473.6</v>
       </c>
       <c r="J203" s="12" t="s">
         <v>104</v>
@@ -9243,10 +9243,10 @@
         <v>195</v>
       </c>
       <c r="H204" s="14">
-        <v>4838.18</v>
+        <v>3407.22</v>
       </c>
       <c r="I204" s="13">
-        <v>387054.4</v>
+        <v>272577.6</v>
       </c>
       <c r="J204" s="12" t="s">
         <v>104</v>
@@ -9275,10 +9275,10 @@
         <v>195</v>
       </c>
       <c r="H205" s="14">
-        <v>4592.44</v>
+        <v>3407.22</v>
       </c>
       <c r="I205" s="13">
-        <v>367395.2</v>
+        <v>272577.6</v>
       </c>
       <c r="J205" s="12" t="s">
         <v>104</v>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="H207" s="18"/>
       <c r="I207" s="13">
-        <v>181494.98</v>
+        <v>179264.68</v>
       </c>
       <c r="J207" s="12" t="s">
         <v>104</v>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="H208" s="18"/>
       <c r="I208" s="13">
-        <v>676404.76</v>
+        <v>652859.14</v>
       </c>
       <c r="J208" s="12" t="s">
         <v>104</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="H210" s="18"/>
       <c r="I210" s="13">
-        <v>129619.77</v>
+        <v>127494.13</v>
       </c>
       <c r="J210" s="12" t="s">
         <v>104</v>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="H212" s="18"/>
       <c r="I212" s="13">
-        <v>243343.78</v>
+        <v>207743.98</v>
       </c>
       <c r="J212" s="12" t="s">
         <v>104</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="H230" s="18"/>
       <c r="I230" s="13">
-        <v>996842.2</v>
+        <v>994968.75</v>
       </c>
       <c r="J230" s="12" t="s">
         <v>104</v>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="H231" s="18"/>
       <c r="I231" s="13">
-        <v>3022740.71</v>
+        <v>3002962.39</v>
       </c>
       <c r="J231" s="12" t="s">
         <v>104</v>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="H233" s="18"/>
       <c r="I233" s="13">
-        <v>650858.51</v>
+        <v>649072.97</v>
       </c>
       <c r="J233" s="12" t="s">
         <v>104</v>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="H234" s="18"/>
       <c r="I234" s="13">
-        <v>20201.57</v>
+        <v>20124.63</v>
       </c>
       <c r="J234" s="12" t="s">
         <v>104</v>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="H235" s="18"/>
       <c r="I235" s="13">
-        <v>2739194.11</v>
+        <v>2712018.36</v>
       </c>
       <c r="J235" s="12" t="s">
         <v>104</v>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="H236" s="18"/>
       <c r="I236" s="13">
-        <v>74401.17</v>
+        <v>74117.8</v>
       </c>
       <c r="J236" s="12" t="s">
         <v>104</v>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="H237" s="18"/>
       <c r="I237" s="13">
-        <v>54506.88</v>
+        <v>54299.27</v>
       </c>
       <c r="J237" s="12" t="s">
         <v>104</v>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="H238" s="18"/>
       <c r="I238" s="13">
-        <v>3852.94</v>
+        <v>3852.48</v>
       </c>
       <c r="J238" s="12" t="s">
         <v>104</v>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="H239" s="18"/>
       <c r="I239" s="13">
-        <v>522432.34</v>
+        <v>519164.26</v>
       </c>
       <c r="J239" s="12" t="s">
         <v>104</v>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="H240" s="18"/>
       <c r="I240" s="13">
-        <v>14190.15</v>
+        <v>14188.44</v>
       </c>
       <c r="J240" s="12" t="s">
         <v>104</v>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="H241" s="18"/>
       <c r="I241" s="13">
-        <v>10395.82</v>
+        <v>10394.56</v>
       </c>
       <c r="J241" s="12" t="s">
         <v>104</v>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="H242" s="18"/>
       <c r="I242" s="13">
-        <v>354564.4</v>
+        <v>349772.54</v>
       </c>
       <c r="J242" s="12" t="s">
         <v>104</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="H243" s="18"/>
       <c r="I243" s="13">
-        <v>553948.83</v>
+        <v>534268.43</v>
       </c>
       <c r="J243" s="12" t="s">
         <v>104</v>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="H244" s="18"/>
       <c r="I244" s="13">
-        <v>119303.97</v>
+        <v>118994.82</v>
       </c>
       <c r="J244" s="12" t="s">
         <v>104</v>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="H245" s="18"/>
       <c r="I245" s="13">
-        <v>186392.93</v>
+        <v>181761.48</v>
       </c>
       <c r="J245" s="12" t="s">
         <v>104</v>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="H246" s="18"/>
       <c r="I246" s="13">
-        <v>627634.88</v>
+        <v>625826.06</v>
       </c>
       <c r="J246" s="12" t="s">
         <v>104</v>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="H247" s="18"/>
       <c r="I247" s="13">
-        <v>165317.25</v>
+        <v>165012.31</v>
       </c>
       <c r="J247" s="12" t="s">
         <v>104</v>
@@ -10514,7 +10514,7 @@
       <c r="G248" s="15"/>
       <c r="H248" s="15"/>
       <c r="I248" s="16">
-        <v>170314234.04</v>
+        <v>168894726.38</v>
       </c>
       <c r="J248" s="15"/>
     </row>
@@ -10613,13 +10613,13 @@
         <v>0</v>
       </c>
       <c r="C6" s="13">
-        <v>9898088.78</v>
+        <v>9427176.38</v>
       </c>
       <c r="D6" s="13">
         <v>5219172.5</v>
       </c>
       <c r="E6" s="13">
-        <v>15668132.53</v>
+        <v>15193948.62</v>
       </c>
       <c r="F6" s="13">
         <v>0</v>
@@ -10639,13 +10639,13 @@
         <v>256761.98</v>
       </c>
       <c r="C7" s="13">
-        <v>325248.73</v>
+        <v>323515.78</v>
       </c>
       <c r="D7" s="13">
         <v>0</v>
       </c>
       <c r="E7" s="13">
-        <v>582010.71</v>
+        <v>580277.76</v>
       </c>
       <c r="F7" s="13">
         <v>0</v>
@@ -10665,13 +10665,13 @@
         <v>766236.6</v>
       </c>
       <c r="C8" s="13">
-        <v>325248.72</v>
+        <v>323515.75</v>
       </c>
       <c r="D8" s="13">
         <v>0</v>
       </c>
       <c r="E8" s="13">
-        <v>1091485.32</v>
+        <v>1089752.35</v>
       </c>
       <c r="F8" s="13">
         <v>0</v>
@@ -10691,13 +10691,13 @@
         <v>1263627.23</v>
       </c>
       <c r="C9" s="13">
-        <v>325248.71</v>
+        <v>323515.74</v>
       </c>
       <c r="D9" s="13">
         <v>0</v>
       </c>
       <c r="E9" s="13">
-        <v>1588875.94</v>
+        <v>1587142.97</v>
       </c>
       <c r="F9" s="13">
         <v>0</v>
@@ -10717,13 +10717,13 @@
         <v>1741089.7</v>
       </c>
       <c r="C10" s="13">
-        <v>325248.76</v>
+        <v>323515.81</v>
       </c>
       <c r="D10" s="13">
         <v>0</v>
       </c>
       <c r="E10" s="13">
-        <v>2066338.46</v>
+        <v>2064605.51</v>
       </c>
       <c r="F10" s="13">
         <v>0</v>
@@ -10743,13 +10743,13 @@
         <v>2191094.19</v>
       </c>
       <c r="C11" s="13">
-        <v>325248.75</v>
+        <v>323515.8</v>
       </c>
       <c r="D11" s="13">
         <v>0</v>
       </c>
       <c r="E11" s="13">
-        <v>2516342.94</v>
+        <v>2514609.99</v>
       </c>
       <c r="F11" s="13">
         <v>0</v>
@@ -10769,13 +10769,13 @@
         <v>2606543.73</v>
       </c>
       <c r="C12" s="13">
-        <v>325248.71</v>
+        <v>323515.74</v>
       </c>
       <c r="D12" s="13">
         <v>0</v>
       </c>
       <c r="E12" s="13">
-        <v>2931792.44</v>
+        <v>2930059.47</v>
       </c>
       <c r="F12" s="13">
         <v>0</v>
@@ -10795,13 +10795,13 @@
         <v>2980886.56</v>
       </c>
       <c r="C13" s="13">
-        <v>325248.93</v>
+        <v>323515.97</v>
       </c>
       <c r="D13" s="13">
         <v>0</v>
       </c>
       <c r="E13" s="13">
-        <v>3306135.49</v>
+        <v>3304402.53</v>
       </c>
       <c r="F13" s="13">
         <v>0</v>
@@ -10821,13 +10821,13 @@
         <v>3308219.05</v>
       </c>
       <c r="C14" s="13">
-        <v>325248.69</v>
+        <v>323515.72</v>
       </c>
       <c r="D14" s="13">
         <v>0</v>
       </c>
       <c r="E14" s="13">
-        <v>3633467.74</v>
+        <v>3631734.77</v>
       </c>
       <c r="F14" s="13">
         <v>0</v>
@@ -10847,22 +10847,22 @@
         <v>3583378.9</v>
       </c>
       <c r="C15" s="13">
-        <v>325248.69</v>
+        <v>323515.72</v>
       </c>
       <c r="D15" s="13">
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <v>3340168.57</v>
+        <v>3610115.57</v>
       </c>
       <c r="F15" s="13">
-        <v>568459.02</v>
+        <v>296779.05</v>
       </c>
       <c r="G15" s="13">
         <v>0</v>
       </c>
       <c r="H15" s="13">
-        <v>568459.02</v>
+        <v>296779.05</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -10873,7 +10873,7 @@
         <v>3802026.81</v>
       </c>
       <c r="C16" s="13">
-        <v>325248.9</v>
+        <v>323515.95</v>
       </c>
       <c r="D16" s="13">
         <v>0</v>
@@ -10882,13 +10882,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="13">
-        <v>4127275.71</v>
+        <v>4125542.76</v>
       </c>
       <c r="G16" s="13">
-        <v>3316.01</v>
+        <v>1731.21</v>
       </c>
       <c r="H16" s="13">
-        <v>4699050.74</v>
+        <v>4424053.02</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -10899,7 +10899,7 @@
         <v>3960714.36</v>
       </c>
       <c r="C17" s="13">
-        <v>325248.69</v>
+        <v>323515.72</v>
       </c>
       <c r="D17" s="13">
         <v>0</v>
@@ -10908,13 +10908,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="13">
-        <v>4285963.05</v>
+        <v>4284230.08</v>
       </c>
       <c r="G17" s="13">
-        <v>27411.13</v>
+        <v>25806.98</v>
       </c>
       <c r="H17" s="13">
-        <v>9012424.92</v>
+        <v>8734090.08</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -10925,7 +10925,7 @@
         <v>4056939.17</v>
       </c>
       <c r="C18" s="13">
-        <v>325248.67</v>
+        <v>323515.7</v>
       </c>
       <c r="D18" s="13">
         <v>0</v>
@@ -10934,13 +10934,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="13">
-        <v>4382187.84</v>
+        <v>4380454.87</v>
       </c>
       <c r="G18" s="13">
-        <v>52572.48</v>
+        <v>50948.86</v>
       </c>
       <c r="H18" s="13">
-        <v>13447185.24</v>
+        <v>13165493.81</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -10951,7 +10951,7 @@
         <v>4089183.64</v>
       </c>
       <c r="C19" s="13">
-        <v>325248.9</v>
+        <v>323515.95</v>
       </c>
       <c r="D19" s="13">
         <v>0</v>
@@ -10960,13 +10960,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="13">
-        <v>4414432.54</v>
+        <v>4412699.59</v>
       </c>
       <c r="G19" s="13">
-        <v>78441.91</v>
+        <v>76798.71</v>
       </c>
       <c r="H19" s="13">
-        <v>17940059.69</v>
+        <v>17654992.11</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -10977,7 +10977,7 @@
         <v>4056939.18</v>
       </c>
       <c r="C20" s="13">
-        <v>325248.87</v>
+        <v>323515.92</v>
       </c>
       <c r="D20" s="13">
         <v>0</v>
@@ -10986,13 +10986,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="13">
-        <v>4382188.05</v>
+        <v>4380455.1</v>
       </c>
       <c r="G20" s="13">
-        <v>104650.35</v>
+        <v>102987.45</v>
       </c>
       <c r="H20" s="13">
-        <v>22426898.09</v>
+        <v>22138434.66</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -11003,7 +11003,7 @@
         <v>3960714.36</v>
       </c>
       <c r="C21" s="13">
-        <v>325248.63</v>
+        <v>323515.67</v>
       </c>
       <c r="D21" s="13">
         <v>0</v>
@@ -11012,13 +11012,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="13">
-        <v>4285962.99</v>
+        <v>4284230.03</v>
       </c>
       <c r="G21" s="13">
-        <v>130823.57</v>
+        <v>129140.87</v>
       </c>
       <c r="H21" s="13">
-        <v>26843684.65</v>
+        <v>26551805.56</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -11029,7 +11029,7 @@
         <v>3802026.76</v>
       </c>
       <c r="C22" s="13">
-        <v>325248.86</v>
+        <v>323515.91</v>
       </c>
       <c r="D22" s="13">
         <v>0</v>
@@ -11038,13 +11038,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="13">
-        <v>4127275.62</v>
+        <v>4125542.67</v>
       </c>
       <c r="G22" s="13">
-        <v>156588.16</v>
+        <v>154885.53</v>
       </c>
       <c r="H22" s="13">
-        <v>31127548.43</v>
+        <v>30832233.76</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -11055,7 +11055,7 @@
         <v>3583378.92</v>
       </c>
       <c r="C23" s="13">
-        <v>325248.84</v>
+        <v>323515.89</v>
       </c>
       <c r="D23" s="13">
         <v>0</v>
@@ -11064,13 +11064,13 @@
         <v>0</v>
       </c>
       <c r="F23" s="13">
-        <v>3908627.76</v>
+        <v>3906894.81</v>
       </c>
       <c r="G23" s="13">
-        <v>181577.37</v>
+        <v>179854.7</v>
       </c>
       <c r="H23" s="13">
-        <v>35217753.56</v>
+        <v>34918983.27</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -11081,7 +11081,7 @@
         <v>3308219.04</v>
       </c>
       <c r="C24" s="13">
-        <v>325248.62</v>
+        <v>323515.66</v>
       </c>
       <c r="D24" s="13">
         <v>0</v>
@@ -11090,13 +11090,13 @@
         <v>0</v>
       </c>
       <c r="F24" s="13">
-        <v>3633467.66</v>
+        <v>3631734.7</v>
       </c>
       <c r="G24" s="13">
-        <v>205436.9</v>
+        <v>203694.07</v>
       </c>
       <c r="H24" s="13">
-        <v>39056658.12</v>
+        <v>38754412.04</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -11107,7 +11107,7 @@
         <v>2980886.55</v>
       </c>
       <c r="C25" s="13">
-        <v>325248.82</v>
+        <v>323515.87</v>
       </c>
       <c r="D25" s="13">
         <v>0</v>
@@ -11116,13 +11116,13 @@
         <v>0</v>
       </c>
       <c r="F25" s="13">
-        <v>3306135.37</v>
+        <v>3304402.42</v>
       </c>
       <c r="G25" s="13">
-        <v>227830.51</v>
+        <v>226067.4</v>
       </c>
       <c r="H25" s="13">
-        <v>42590624</v>
+        <v>42284881.86</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -11133,7 +11133,7 @@
         <v>2606543.76</v>
       </c>
       <c r="C26" s="13">
-        <v>325248.82</v>
+        <v>323515.87</v>
       </c>
       <c r="D26" s="13">
         <v>0</v>
@@ -11142,13 +11142,13 @@
         <v>0</v>
       </c>
       <c r="F26" s="13">
-        <v>2931792.58</v>
+        <v>2930059.63</v>
       </c>
       <c r="G26" s="13">
-        <v>248445.31</v>
+        <v>246661.81</v>
       </c>
       <c r="H26" s="13">
-        <v>45770861.89</v>
+        <v>45461603.3</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -11159,7 +11159,7 @@
         <v>2191094.17</v>
       </c>
       <c r="C27" s="13">
-        <v>325248.61</v>
+        <v>323515.65</v>
       </c>
       <c r="D27" s="13">
         <v>0</v>
@@ -11168,13 +11168,13 @@
         <v>0</v>
       </c>
       <c r="F27" s="13">
-        <v>2516342.78</v>
+        <v>2514609.82</v>
       </c>
       <c r="G27" s="13">
-        <v>266996.69</v>
+        <v>265192.69</v>
       </c>
       <c r="H27" s="13">
-        <v>48554201.36</v>
+        <v>48241405.81</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -11185,7 +11185,7 @@
         <v>1741089.69</v>
       </c>
       <c r="C28" s="13">
-        <v>325248.8</v>
+        <v>323515.85</v>
       </c>
       <c r="D28" s="13">
         <v>0</v>
@@ -11194,13 +11194,13 @@
         <v>0</v>
       </c>
       <c r="F28" s="13">
-        <v>2066338.49</v>
+        <v>2064605.54</v>
       </c>
       <c r="G28" s="13">
-        <v>283232.84</v>
+        <v>281408.2</v>
       </c>
       <c r="H28" s="13">
-        <v>50903772.69</v>
+        <v>50587419.55</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -11211,7 +11211,7 @@
         <v>1263627.26</v>
       </c>
       <c r="C29" s="13">
-        <v>325248.8</v>
+        <v>323515.85</v>
       </c>
       <c r="D29" s="13">
         <v>0</v>
@@ -11220,13 +11220,13 @@
         <v>0</v>
       </c>
       <c r="F29" s="13">
-        <v>1588876.06</v>
+        <v>1587143.11</v>
       </c>
       <c r="G29" s="13">
-        <v>296938.67</v>
+        <v>295093.28</v>
       </c>
       <c r="H29" s="13">
-        <v>52789587.42</v>
+        <v>52469655.94</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -11237,7 +11237,7 @@
         <v>766236.57</v>
       </c>
       <c r="C30" s="13">
-        <v>325248.61</v>
+        <v>323515.65</v>
       </c>
       <c r="D30" s="13">
         <v>0</v>
@@ -11246,13 +11246,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="13">
-        <v>1091485.18</v>
+        <v>1089752.22</v>
       </c>
       <c r="G30" s="13">
-        <v>307939.26</v>
+        <v>306072.99</v>
       </c>
       <c r="H30" s="13">
-        <v>54189011.86</v>
+        <v>53865481.15</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -11263,7 +11263,7 @@
         <v>256761.99</v>
       </c>
       <c r="C31" s="13">
-        <v>325248.8</v>
+        <v>323515.85</v>
       </c>
       <c r="D31" s="13">
         <v>0</v>
@@ -11272,13 +11272,13 @@
         <v>0</v>
       </c>
       <c r="F31" s="13">
-        <v>582010.79</v>
+        <v>580277.84</v>
       </c>
       <c r="G31" s="13">
-        <v>316102.57</v>
+        <v>314215.31</v>
       </c>
       <c r="H31" s="13">
-        <v>55087125.22</v>
+        <v>54759974.3</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -11327,13 +11327,13 @@
         <v>0</v>
       </c>
       <c r="C34" s="13">
-        <v>5371356.23</v>
+        <v>4616847.31</v>
       </c>
       <c r="D34" s="13">
         <v>5039401</v>
       </c>
       <c r="E34" s="13">
-        <v>10716454.13</v>
+        <v>9957004.61</v>
       </c>
       <c r="F34" s="13">
         <v>0</v>
@@ -11353,13 +11353,13 @@
         <v>453172.57</v>
       </c>
       <c r="C35" s="13">
-        <v>226782.13</v>
+        <v>223959.92</v>
       </c>
       <c r="D35" s="13">
         <v>0</v>
       </c>
       <c r="E35" s="13">
-        <v>679954.7</v>
+        <v>677132.49</v>
       </c>
       <c r="F35" s="13">
         <v>0</v>
@@ -11379,13 +11379,13 @@
         <v>1336793.71</v>
       </c>
       <c r="C36" s="13">
-        <v>226782.12</v>
+        <v>223959.91</v>
       </c>
       <c r="D36" s="13">
         <v>0</v>
       </c>
       <c r="E36" s="13">
-        <v>1563575.83</v>
+        <v>1560753.62</v>
       </c>
       <c r="F36" s="13">
         <v>0</v>
@@ -11405,13 +11405,13 @@
         <v>2153382.4</v>
       </c>
       <c r="C37" s="13">
-        <v>226782.11</v>
+        <v>223959.9</v>
       </c>
       <c r="D37" s="13">
         <v>0</v>
       </c>
       <c r="E37" s="13">
-        <v>2380164.51</v>
+        <v>2377342.3</v>
       </c>
       <c r="F37" s="13">
         <v>0</v>
@@ -11431,13 +11431,13 @@
         <v>2861991.55</v>
       </c>
       <c r="C38" s="13">
-        <v>226782.07</v>
+        <v>223959.86</v>
       </c>
       <c r="D38" s="13">
         <v>0</v>
       </c>
       <c r="E38" s="13">
-        <v>3088773.62</v>
+        <v>3085951.41</v>
       </c>
       <c r="F38" s="13">
         <v>0</v>
@@ -11457,22 +11457,22 @@
         <v>3427088.53</v>
       </c>
       <c r="C39" s="13">
-        <v>226782.14</v>
+        <v>223959.93</v>
       </c>
       <c r="D39" s="13">
         <v>0</v>
       </c>
       <c r="E39" s="13">
-        <v>1950870.39</v>
+        <v>2392235.65</v>
       </c>
       <c r="F39" s="13">
-        <v>1703000.28</v>
+        <v>1258812.81</v>
       </c>
       <c r="G39" s="13">
         <v>0</v>
       </c>
       <c r="H39" s="13">
-        <v>1703000.28</v>
+        <v>1258812.81</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -11483,7 +11483,7 @@
         <v>3820336.88</v>
       </c>
       <c r="C40" s="13">
-        <v>226782.06</v>
+        <v>223959.84</v>
       </c>
       <c r="D40" s="13">
         <v>0</v>
@@ -11492,13 +11492,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="13">
-        <v>4047118.94</v>
+        <v>4044296.72</v>
       </c>
       <c r="G40" s="13">
-        <v>9934.17</v>
+        <v>7343.07</v>
       </c>
       <c r="H40" s="13">
-        <v>5760053.39</v>
+        <v>5310452.6</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -11509,7 +11509,7 @@
         <v>4022017.64</v>
       </c>
       <c r="C41" s="13">
-        <v>226782.13</v>
+        <v>223959.92</v>
       </c>
       <c r="D41" s="13">
         <v>0</v>
@@ -11518,13 +11518,13 @@
         <v>0</v>
       </c>
       <c r="F41" s="13">
-        <v>4248799.77</v>
+        <v>4245977.56</v>
       </c>
       <c r="G41" s="13">
-        <v>33600.31</v>
+        <v>30977.64</v>
       </c>
       <c r="H41" s="13">
-        <v>10042453.47</v>
+        <v>9587407.8</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -11535,7 +11535,7 @@
         <v>4022017.72</v>
       </c>
       <c r="C42" s="13">
-        <v>226782.03</v>
+        <v>223959.81</v>
       </c>
       <c r="D42" s="13">
         <v>0</v>
@@ -11544,13 +11544,13 @@
         <v>0</v>
       </c>
       <c r="F42" s="13">
-        <v>4248799.75</v>
+        <v>4245977.53</v>
       </c>
       <c r="G42" s="13">
-        <v>58580.98</v>
+        <v>55926.55</v>
       </c>
       <c r="H42" s="13">
-        <v>14349834.2</v>
+        <v>13889311.88</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -11561,7 +11561,7 @@
         <v>3820336.84</v>
       </c>
       <c r="C43" s="13">
-        <v>226782.15</v>
+        <v>223959.94</v>
       </c>
       <c r="D43" s="13">
         <v>0</v>
@@ -11570,13 +11570,13 @@
         <v>0</v>
       </c>
       <c r="F43" s="13">
-        <v>4047118.99</v>
+        <v>4044296.78</v>
       </c>
       <c r="G43" s="13">
-        <v>83707.37</v>
+        <v>81020.99</v>
       </c>
       <c r="H43" s="13">
-        <v>18480660.56</v>
+        <v>18014629.65</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -11587,7 +11587,7 @@
         <v>3427088.51</v>
       </c>
       <c r="C44" s="13">
-        <v>226782.01</v>
+        <v>223959.79</v>
       </c>
       <c r="D44" s="13">
         <v>0</v>
@@ -11596,13 +11596,13 @@
         <v>0</v>
       </c>
       <c r="F44" s="13">
-        <v>3653870.52</v>
+        <v>3651048.3</v>
       </c>
       <c r="G44" s="13">
-        <v>107803.85</v>
+        <v>105085.34</v>
       </c>
       <c r="H44" s="13">
-        <v>22242334.93</v>
+        <v>21770763.29</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -11613,7 +11613,7 @@
         <v>2861991.56</v>
       </c>
       <c r="C45" s="13">
-        <v>226782.01</v>
+        <v>223959.79</v>
       </c>
       <c r="D45" s="13">
         <v>0</v>
@@ -11622,13 +11622,13 @@
         <v>0</v>
       </c>
       <c r="F45" s="13">
-        <v>3088773.57</v>
+        <v>3085951.35</v>
       </c>
       <c r="G45" s="13">
-        <v>129746.95</v>
+        <v>126996.12</v>
       </c>
       <c r="H45" s="13">
-        <v>25460855.45</v>
+        <v>24983710.76</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -11639,7 +11639,7 @@
         <v>2153382.37</v>
       </c>
       <c r="C46" s="13">
-        <v>226781.99</v>
+        <v>223959.78</v>
       </c>
       <c r="D46" s="13">
         <v>0</v>
@@ -11648,13 +11648,13 @@
         <v>0</v>
       </c>
       <c r="F46" s="13">
-        <v>2380164.36</v>
+        <v>2377342.15</v>
       </c>
       <c r="G46" s="13">
-        <v>148521.66</v>
+        <v>145738.31</v>
       </c>
       <c r="H46" s="13">
-        <v>27989541.47</v>
+        <v>27506791.22</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -11665,7 +11665,7 @@
         <v>1336793.67</v>
       </c>
       <c r="C47" s="13">
-        <v>226782.15</v>
+        <v>223959.94</v>
       </c>
       <c r="D47" s="13">
         <v>0</v>
@@ -11674,13 +11674,13 @@
         <v>0</v>
       </c>
       <c r="F47" s="13">
-        <v>1563575.82</v>
+        <v>1560753.61</v>
       </c>
       <c r="G47" s="13">
-        <v>163272.33</v>
+        <v>160456.28</v>
       </c>
       <c r="H47" s="13">
-        <v>29716389.62</v>
+        <v>29228001.11</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -11691,7 +11691,7 @@
         <v>453172.57</v>
       </c>
       <c r="C48" s="13">
-        <v>226781.98</v>
+        <v>223959.77</v>
       </c>
       <c r="D48" s="13">
         <v>0</v>
@@ -11700,13 +11700,13 @@
         <v>0</v>
       </c>
       <c r="F48" s="13">
-        <v>679954.55</v>
+        <v>677132.34</v>
       </c>
       <c r="G48" s="13">
-        <v>173345.61</v>
+        <v>170496.67</v>
       </c>
       <c r="H48" s="13">
-        <v>30569689.78</v>
+        <v>30075630.12</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -11755,13 +11755,13 @@
         <v>0</v>
       </c>
       <c r="C51" s="13">
-        <v>2343223.49</v>
+        <v>2298617.62</v>
       </c>
       <c r="D51" s="13">
         <v>842026.5</v>
       </c>
       <c r="E51" s="13">
-        <v>3350567.24</v>
+        <v>3305656.43</v>
       </c>
       <c r="F51" s="13">
         <v>0</v>
@@ -11781,13 +11781,13 @@
         <v>143856.4</v>
       </c>
       <c r="C52" s="13">
-        <v>130491.99</v>
+        <v>130276.01</v>
       </c>
       <c r="D52" s="13">
         <v>0</v>
       </c>
       <c r="E52" s="13">
-        <v>274348.39</v>
+        <v>274132.41</v>
       </c>
       <c r="F52" s="13">
         <v>0</v>
@@ -11807,13 +11807,13 @@
         <v>427645.06</v>
       </c>
       <c r="C53" s="13">
-        <v>130491.99</v>
+        <v>130276</v>
       </c>
       <c r="D53" s="13">
         <v>0</v>
       </c>
       <c r="E53" s="13">
-        <v>558137.05</v>
+        <v>557921.06</v>
       </c>
       <c r="F53" s="13">
         <v>0</v>
@@ -11833,13 +11833,13 @@
         <v>699768.82</v>
       </c>
       <c r="C54" s="13">
-        <v>130491.99</v>
+        <v>130276</v>
       </c>
       <c r="D54" s="13">
         <v>0</v>
       </c>
       <c r="E54" s="13">
-        <v>830260.81</v>
+        <v>830044.82</v>
       </c>
       <c r="F54" s="13">
         <v>0</v>
@@ -11859,13 +11859,13 @@
         <v>952804.59</v>
       </c>
       <c r="C55" s="13">
-        <v>130491.98</v>
+        <v>130275.99</v>
       </c>
       <c r="D55" s="13">
         <v>0</v>
       </c>
       <c r="E55" s="13">
-        <v>1083296.57</v>
+        <v>1083080.58</v>
       </c>
       <c r="F55" s="13">
         <v>0</v>
@@ -11885,13 +11885,13 @@
         <v>1179850.39</v>
       </c>
       <c r="C56" s="13">
-        <v>130491.98</v>
+        <v>130275.99</v>
       </c>
       <c r="D56" s="13">
         <v>0</v>
       </c>
       <c r="E56" s="13">
-        <v>1310342.37</v>
+        <v>1310126.38</v>
       </c>
       <c r="F56" s="13">
         <v>0</v>
@@ -11911,13 +11911,13 @@
         <v>1374712.89</v>
       </c>
       <c r="C57" s="13">
-        <v>130491.98</v>
+        <v>130275.99</v>
       </c>
       <c r="D57" s="13">
         <v>0</v>
       </c>
       <c r="E57" s="13">
-        <v>1505204.87</v>
+        <v>1504988.88</v>
       </c>
       <c r="F57" s="13">
         <v>0</v>
@@ -11937,13 +11937,13 @@
         <v>1532076.88</v>
       </c>
       <c r="C58" s="13">
-        <v>130491.96</v>
+        <v>130275.97</v>
       </c>
       <c r="D58" s="13">
         <v>0</v>
       </c>
       <c r="E58" s="13">
-        <v>1662568.84</v>
+        <v>1662352.85</v>
       </c>
       <c r="F58" s="13">
         <v>0</v>
@@ -11963,22 +11963,22 @@
         <v>1647649.83</v>
       </c>
       <c r="C59" s="13">
-        <v>130491.96</v>
+        <v>130275.96</v>
       </c>
       <c r="D59" s="13">
         <v>0</v>
       </c>
       <c r="E59" s="13">
-        <v>446424.15</v>
+        <v>472517.53</v>
       </c>
       <c r="F59" s="13">
-        <v>1331717.64</v>
+        <v>1305408.26</v>
       </c>
       <c r="G59" s="13">
         <v>0</v>
       </c>
       <c r="H59" s="13">
-        <v>1331717.64</v>
+        <v>1305408.26</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -11989,7 +11989,7 @@
         <v>1718279.1</v>
       </c>
       <c r="C60" s="13">
-        <v>130491.95</v>
+        <v>130275.95</v>
       </c>
       <c r="D60" s="13">
         <v>0</v>
@@ -11998,13 +11998,13 @@
         <v>0</v>
       </c>
       <c r="F60" s="13">
-        <v>1848771.05</v>
+        <v>1848555.05</v>
       </c>
       <c r="G60" s="13">
-        <v>7768.35</v>
+        <v>7614.88</v>
       </c>
       <c r="H60" s="13">
-        <v>3188257.04</v>
+        <v>3161578.19</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -12015,7 +12015,7 @@
         <v>1742038.26</v>
       </c>
       <c r="C61" s="13">
-        <v>130491.94</v>
+        <v>130275.95</v>
       </c>
       <c r="D61" s="13">
         <v>0</v>
@@ -12024,13 +12024,13 @@
         <v>0</v>
       </c>
       <c r="F61" s="13">
-        <v>1872530.2</v>
+        <v>1872314.21</v>
       </c>
       <c r="G61" s="13">
-        <v>18598.17</v>
+        <v>18442.54</v>
       </c>
       <c r="H61" s="13">
-        <v>5079385.41</v>
+        <v>5052334.94</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -12041,7 +12041,7 @@
         <v>1718279.1</v>
       </c>
       <c r="C62" s="13">
-        <v>130492</v>
+        <v>130276.02</v>
       </c>
       <c r="D62" s="13">
         <v>0</v>
@@ -12050,13 +12050,13 @@
         <v>0</v>
       </c>
       <c r="F62" s="13">
-        <v>1848771.1</v>
+        <v>1848555.12</v>
       </c>
       <c r="G62" s="13">
-        <v>29629.75</v>
+        <v>29471.95</v>
       </c>
       <c r="H62" s="13">
-        <v>6957786.26</v>
+        <v>6930362.01</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -12067,7 +12067,7 @@
         <v>1647649.83</v>
       </c>
       <c r="C63" s="13">
-        <v>130491.94</v>
+        <v>130275.95</v>
       </c>
       <c r="D63" s="13">
         <v>0</v>
@@ -12076,13 +12076,13 @@
         <v>0</v>
       </c>
       <c r="F63" s="13">
-        <v>1778141.77</v>
+        <v>1777925.78</v>
       </c>
       <c r="G63" s="13">
-        <v>40587.09</v>
+        <v>40427.11</v>
       </c>
       <c r="H63" s="13">
-        <v>8776515.12</v>
+        <v>8748714.9</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -12093,7 +12093,7 @@
         <v>1532076.88</v>
       </c>
       <c r="C64" s="13">
-        <v>130492</v>
+        <v>130276.02</v>
       </c>
       <c r="D64" s="13">
         <v>0</v>
@@ -12102,13 +12102,13 @@
         <v>0</v>
       </c>
       <c r="F64" s="13">
-        <v>1662568.88</v>
+        <v>1662352.9</v>
       </c>
       <c r="G64" s="13">
-        <v>51196.34</v>
+        <v>51034.17</v>
       </c>
       <c r="H64" s="13">
-        <v>10490280.34</v>
+        <v>10462101.97</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -12119,7 +12119,7 @@
         <v>1374712.89</v>
       </c>
       <c r="C65" s="13">
-        <v>130491.94</v>
+        <v>130275.95</v>
       </c>
       <c r="D65" s="13">
         <v>0</v>
@@ -12128,13 +12128,13 @@
         <v>0</v>
       </c>
       <c r="F65" s="13">
-        <v>1505204.83</v>
+        <v>1504988.84</v>
       </c>
       <c r="G65" s="13">
-        <v>61193.3</v>
+        <v>61028.93</v>
       </c>
       <c r="H65" s="13">
-        <v>12056678.47</v>
+        <v>12028119.74</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -12145,7 +12145,7 @@
         <v>1179850.42</v>
       </c>
       <c r="C66" s="13">
-        <v>130492</v>
+        <v>130276.02</v>
       </c>
       <c r="D66" s="13">
         <v>0</v>
@@ -12154,13 +12154,13 @@
         <v>0</v>
       </c>
       <c r="F66" s="13">
-        <v>1310342.42</v>
+        <v>1310126.44</v>
       </c>
       <c r="G66" s="13">
-        <v>70330.62</v>
+        <v>70164.03</v>
       </c>
       <c r="H66" s="13">
-        <v>13437351.51</v>
+        <v>13408410.21</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -12171,7 +12171,7 @@
         <v>952804.59</v>
       </c>
       <c r="C67" s="13">
-        <v>130491.92</v>
+        <v>130275.94</v>
       </c>
       <c r="D67" s="13">
         <v>0</v>
@@ -12180,13 +12180,13 @@
         <v>0</v>
       </c>
       <c r="F67" s="13">
-        <v>1083296.51</v>
+        <v>1083080.53</v>
       </c>
       <c r="G67" s="13">
-        <v>78384.55</v>
+        <v>78215.73</v>
       </c>
       <c r="H67" s="13">
-        <v>14599032.57</v>
+        <v>14569706.47</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -12197,7 +12197,7 @@
         <v>699768.79</v>
       </c>
       <c r="C68" s="13">
-        <v>130492</v>
+        <v>130276.02</v>
       </c>
       <c r="D68" s="13">
         <v>0</v>
@@ -12206,13 +12206,13 @@
         <v>0</v>
       </c>
       <c r="F68" s="13">
-        <v>830260.79</v>
+        <v>830044.81</v>
       </c>
       <c r="G68" s="13">
-        <v>85161.02</v>
+        <v>84989.95</v>
       </c>
       <c r="H68" s="13">
-        <v>15514454.38</v>
+        <v>15484741.23</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -12223,7 +12223,7 @@
         <v>427645.06</v>
       </c>
       <c r="C69" s="13">
-        <v>130491.92</v>
+        <v>130275.94</v>
       </c>
       <c r="D69" s="13">
         <v>0</v>
@@ -12232,13 +12232,13 @@
         <v>0</v>
       </c>
       <c r="F69" s="13">
-        <v>558136.98</v>
+        <v>557921</v>
       </c>
       <c r="G69" s="13">
-        <v>90500.98</v>
+        <v>90327.66</v>
       </c>
       <c r="H69" s="13">
-        <v>16163092.34</v>
+        <v>16132989.89</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -12249,7 +12249,7 @@
         <v>143856.38</v>
       </c>
       <c r="C70" s="13">
-        <v>130492</v>
+        <v>130276.02</v>
       </c>
       <c r="D70" s="13">
         <v>0</v>
@@ -12258,13 +12258,13 @@
         <v>0</v>
       </c>
       <c r="F70" s="13">
-        <v>274348.38</v>
+        <v>274132.4</v>
       </c>
       <c r="G70" s="13">
-        <v>94284.71</v>
+        <v>94109.11</v>
       </c>
       <c r="H70" s="13">
-        <v>16531725.43</v>
+        <v>16501231.4</v>
       </c>
     </row>
   </sheetData>
